--- a/04_Figures/F04_association/modules/T1/lm/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T1/lm/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8.64625200269644</v>
+        <v>-2.85428938914271</v>
       </c>
       <c r="E2" t="n">
-        <v>0.671463954731289</v>
+        <v>-0.181581203689759</v>
       </c>
       <c r="F2" t="n">
-        <v>0.51368042717557</v>
+        <v>0.858712033263658</v>
       </c>
       <c r="G2" t="n">
-        <v>0.894707259344725</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.49900680693278</v>
+        <v>38.2478442578955</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.202071772402321</v>
+        <v>1.26309912315202</v>
       </c>
       <c r="F3" t="n">
-        <v>0.842988516188581</v>
+        <v>0.228738320505704</v>
       </c>
       <c r="G3" t="n">
-        <v>0.910321217687824</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-19.5680125627125</v>
+        <v>2.33404458550465</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.06469660760303</v>
+        <v>0.145141691243844</v>
       </c>
       <c r="F4" t="n">
-        <v>0.30638978609643</v>
+        <v>0.886825191195831</v>
       </c>
       <c r="G4" t="n">
-        <v>0.804559374478125</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>36.1466932409309</v>
+        <v>1.61992108451257</v>
       </c>
       <c r="E5" t="n">
-        <v>1.05771204875681</v>
+        <v>0.120783389817103</v>
       </c>
       <c r="F5" t="n">
-        <v>0.309445913260817</v>
+        <v>0.905709481952858</v>
       </c>
       <c r="G5" t="n">
-        <v>0.804559374478125</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-12.9975652225037</v>
+        <v>-14.768973223428</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.902950172005502</v>
+        <v>-1.03162825601319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.382978723471973</v>
+        <v>0.321057950514642</v>
       </c>
       <c r="G6" t="n">
-        <v>0.829787234189275</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>20.0433941768137</v>
+        <v>8.19389507147535</v>
       </c>
       <c r="E7" t="n">
-        <v>1.51845369702192</v>
+        <v>0.635886898039375</v>
       </c>
       <c r="F7" t="n">
-        <v>0.152839070121221</v>
+        <v>0.535884837690526</v>
       </c>
       <c r="G7" t="n">
-        <v>0.804559374478125</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>5.52931849089197</v>
+        <v>11.3033226318984</v>
       </c>
       <c r="E8" t="n">
-        <v>0.365240553894968</v>
+        <v>0.63079792967965</v>
       </c>
       <c r="F8" t="n">
-        <v>0.720805456210623</v>
+        <v>0.539104728317532</v>
       </c>
       <c r="G8" t="n">
-        <v>0.910321217687824</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>3.74846216583047</v>
+        <v>5.63478078744047</v>
       </c>
       <c r="E9" t="n">
-        <v>0.223468103774318</v>
+        <v>0.423518593586925</v>
       </c>
       <c r="F9" t="n">
-        <v>0.826644489641121</v>
+        <v>0.678839981726146</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910321217687824</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5325374116449</v>
+        <v>6.06683171093717</v>
       </c>
       <c r="E10" t="n">
-        <v>0.114847130228041</v>
+        <v>0.512769328549746</v>
       </c>
       <c r="F10" t="n">
-        <v>0.910321217687824</v>
+        <v>0.616714065661877</v>
       </c>
       <c r="G10" t="n">
-        <v>0.910321217687824</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>22.0952267556702</v>
+        <v>-7.47134685496238</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1193831064179</v>
+        <v>-0.494427491914566</v>
       </c>
       <c r="F11" t="n">
-        <v>0.283233168061323</v>
+        <v>0.629254097202836</v>
       </c>
       <c r="G11" t="n">
-        <v>0.804559374478125</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>25.4835683357691</v>
+        <v>-18.83134195762</v>
       </c>
       <c r="E12" t="n">
-        <v>1.30943499562649</v>
+        <v>-1.03203200856847</v>
       </c>
       <c r="F12" t="n">
-        <v>0.21305804606349</v>
+        <v>0.320875809560466</v>
       </c>
       <c r="G12" t="n">
-        <v>0.804559374478125</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-8.11908559149368</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.538874477860791</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.599080716982251</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.894707259344725</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6.71341633688689</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.508806919655176</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.619412718007886</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.894707259344725</v>
+        <v>0.905709481952858</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1794.60543347749</v>
+        <v>575.066832370107</v>
       </c>
       <c r="E2" t="n">
-        <v>0.849191750838677</v>
+        <v>0.220839342274521</v>
       </c>
       <c r="F2" t="n">
-        <v>0.411140171138718</v>
+        <v>0.828648169172143</v>
       </c>
       <c r="G2" t="n">
-        <v>0.890803704133889</v>
+        <v>0.93989000624409</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-787.806929111346</v>
+        <v>3289.45256580555</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.274839997626136</v>
+        <v>0.627805921091497</v>
       </c>
       <c r="F3" t="n">
-        <v>0.787758574257745</v>
+        <v>0.541002884387972</v>
       </c>
       <c r="G3" t="n">
-        <v>0.92200485328431</v>
+        <v>0.93989000624409</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-4443.82383590803</v>
+        <v>-498.554043606967</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.51786583121418</v>
+        <v>-0.187132839558781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.152985855462283</v>
+        <v>0.8544454602219</v>
       </c>
       <c r="G4" t="n">
-        <v>0.754092025046147</v>
+        <v>0.93989000624409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>2204.69020766593</v>
+        <v>-1046.10887674005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.375477888351732</v>
+        <v>-0.474345846459185</v>
       </c>
       <c r="F5" t="n">
-        <v>0.713360308890119</v>
+        <v>0.643122004285323</v>
       </c>
       <c r="G5" t="n">
-        <v>0.92200485328431</v>
+        <v>0.93989000624409</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-198.426255653103</v>
+        <v>-499.983329040964</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0806906176156364</v>
+        <v>-0.202885206979367</v>
       </c>
       <c r="F6" t="n">
-        <v>0.936917013736413</v>
+        <v>0.842365718752366</v>
       </c>
       <c r="G6" t="n">
-        <v>0.936917013736413</v>
+        <v>0.93989000624409</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>3493.09615240981</v>
+        <v>1768.36501243462</v>
       </c>
       <c r="E7" t="n">
-        <v>1.61161425572138</v>
+        <v>0.837009135636355</v>
       </c>
       <c r="F7" t="n">
-        <v>0.131047791560788</v>
+        <v>0.417709126459331</v>
       </c>
       <c r="G7" t="n">
-        <v>0.754092025046147</v>
+        <v>0.93989000624409</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>2128.27249240115</v>
+        <v>3806.26621916462</v>
       </c>
       <c r="E8" t="n">
-        <v>0.867902503732627</v>
+        <v>1.34757124198204</v>
       </c>
       <c r="F8" t="n">
-        <v>0.401185564120612</v>
+        <v>0.200813496723971</v>
       </c>
       <c r="G8" t="n">
-        <v>0.890803704133889</v>
+        <v>0.93989000624409</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>2707.02847607487</v>
+        <v>1481.12379298427</v>
       </c>
       <c r="E9" t="n">
-        <v>1.00906590159922</v>
+        <v>0.678726865375694</v>
       </c>
       <c r="F9" t="n">
-        <v>0.331356506265728</v>
+        <v>0.509214065304581</v>
       </c>
       <c r="G9" t="n">
-        <v>0.890803704133889</v>
+        <v>0.93989000624409</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-1097.00373656133</v>
+        <v>29.9976829502581</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.500452449542257</v>
+        <v>0.0151434806535441</v>
       </c>
       <c r="F10" t="n">
-        <v>0.62512145149917</v>
+        <v>0.988147655803604</v>
       </c>
       <c r="G10" t="n">
-        <v>0.92200485328431</v>
+        <v>0.988147655803604</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>4576.45435085514</v>
+        <v>-1011.2667762308</v>
       </c>
       <c r="E11" t="n">
-        <v>1.43817210932041</v>
+        <v>-0.402471555026062</v>
       </c>
       <c r="F11" t="n">
-        <v>0.174021236549111</v>
+        <v>0.693876708380057</v>
       </c>
       <c r="G11" t="n">
-        <v>0.754092025046147</v>
+        <v>0.93989000624409</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>2229.13831586436</v>
+        <v>-4159.92439668538</v>
       </c>
       <c r="E12" t="n">
-        <v>0.66030315486376</v>
+        <v>-1.42129552654654</v>
       </c>
       <c r="F12" t="n">
-        <v>0.520588072799479</v>
+        <v>0.178773699224712</v>
       </c>
       <c r="G12" t="n">
-        <v>0.92200485328431</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-1090.67456596477</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.435050250121535</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.670661108040658</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.92200485328431</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>422.415711784709</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.191514490645141</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.851081403031671</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.92200485328431</v>
+        <v>0.93989000624409</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1573.79885357699</v>
+        <v>674.125684361149</v>
       </c>
       <c r="E2" t="n">
-        <v>0.794220451028536</v>
+        <v>0.27730395120494</v>
       </c>
       <c r="F2" t="n">
-        <v>0.441324958811552</v>
+        <v>0.785907355403106</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6829952848431</v>
+        <v>0.88978526878848</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-590.33874651095</v>
+        <v>4783.52594683632</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.22014093748895</v>
+        <v>0.998627312176802</v>
       </c>
       <c r="F3" t="n">
-        <v>0.82918071373523</v>
+        <v>0.336201268197821</v>
       </c>
       <c r="G3" t="n">
-        <v>0.82918071373523</v>
+        <v>0.819453520840434</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-4957.76537015275</v>
+        <v>-352.063154231421</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.88434063942345</v>
+        <v>-0.141317843742412</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0820741026350046</v>
+        <v>0.88978526878848</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6829952848431</v>
+        <v>0.88978526878848</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>4415.70232088273</v>
+        <v>-1592.98233121479</v>
       </c>
       <c r="E5" t="n">
-        <v>0.82083579992144</v>
+        <v>-0.784204265943173</v>
       </c>
       <c r="F5" t="n">
-        <v>0.426536178548576</v>
+        <v>0.446974647731146</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6829952848431</v>
+        <v>0.819453520840434</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-1135.21981777443</v>
+        <v>-1368.45537575319</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.498536471803734</v>
+        <v>-0.601434125281911</v>
       </c>
       <c r="F6" t="n">
-        <v>0.626434240971541</v>
+        <v>0.557893639984578</v>
       </c>
       <c r="G6" t="n">
-        <v>0.740947635940212</v>
+        <v>0.876690005690052</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>3438.81434456015</v>
+        <v>1556.84903954256</v>
       </c>
       <c r="E7" t="n">
-        <v>1.71655429255487</v>
+        <v>0.786105409385012</v>
       </c>
       <c r="F7" t="n">
-        <v>0.109776300051886</v>
+        <v>0.445898768702992</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6829952848431</v>
+        <v>0.819453520840434</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>2228.65335542619</v>
+        <v>3321.71145459607</v>
       </c>
       <c r="E8" t="n">
-        <v>0.979747612425923</v>
+        <v>1.24725407797158</v>
       </c>
       <c r="F8" t="n">
-        <v>0.345092737392942</v>
+        <v>0.234306829612491</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6829952848431</v>
+        <v>0.819453520840434</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>2231.30053152663</v>
+        <v>1907.73633472951</v>
       </c>
       <c r="E9" t="n">
-        <v>0.882325569614676</v>
+        <v>0.950704488116115</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3936234811146</v>
+        <v>0.359095829237634</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6829952848431</v>
+        <v>0.819453520840434</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-1630.96723942879</v>
+        <v>392.594318272861</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.808145779700839</v>
+        <v>0.212432103470741</v>
       </c>
       <c r="F10" t="n">
-        <v>0.433546712820783</v>
+        <v>0.835064598455908</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6829952848431</v>
+        <v>0.88978526878848</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>4417.97266840108</v>
+        <v>-804.617225869237</v>
       </c>
       <c r="E11" t="n">
-        <v>1.49355642340957</v>
+        <v>-0.342062104804679</v>
       </c>
       <c r="F11" t="n">
-        <v>0.159161449903028</v>
+        <v>0.737770861806192</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6829952848431</v>
+        <v>0.88978526878848</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>2323.08638492898</v>
+        <v>-4758.11414942414</v>
       </c>
       <c r="E12" t="n">
-        <v>0.739335618028941</v>
+        <v>-1.8109592010132</v>
       </c>
       <c r="F12" t="n">
-        <v>0.472842889506761</v>
+        <v>0.0933075655049885</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6829952848431</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-881.204599760372</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.375416448050943</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.713404901555961</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.772855310018958</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1017.8757264525</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.497775966112762</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.62695569194941</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.740947635940212</v>
+        <v>0.819453520840434</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.23305686849639</v>
+        <v>-3.70489127356995</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.457157811942528</v>
+        <v>-1.19466602340532</v>
       </c>
       <c r="F2" t="n">
-        <v>0.655103443971186</v>
+        <v>0.253559170687692</v>
       </c>
       <c r="G2" t="n">
-        <v>0.964465848514953</v>
+        <v>0.595587174417968</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.13485190148563</v>
+        <v>8.70677142109232</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.316456401166918</v>
+        <v>1.40276913454382</v>
       </c>
       <c r="F3" t="n">
-        <v>0.756680146889582</v>
+        <v>0.184114521488118</v>
       </c>
       <c r="G3" t="n">
-        <v>0.964465848514953</v>
+        <v>0.595587174417968</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>3.25652010388715</v>
+        <v>1.03696410601172</v>
       </c>
       <c r="E4" t="n">
-        <v>0.840622267488198</v>
+        <v>0.311558055348735</v>
       </c>
       <c r="F4" t="n">
-        <v>0.415753714216574</v>
+        <v>0.760316571922812</v>
       </c>
       <c r="G4" t="n">
-        <v>0.772114040687924</v>
+        <v>0.836348229115094</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10.1388760669559</v>
+        <v>4.25677596157532</v>
       </c>
       <c r="E5" t="n">
-        <v>1.48295781367867</v>
+        <v>1.68724480646101</v>
       </c>
       <c r="F5" t="n">
-        <v>0.161919268601432</v>
+        <v>0.115388471957728</v>
       </c>
       <c r="G5" t="n">
-        <v>0.44265171507161</v>
+        <v>0.595587174417968</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.97429593708162</v>
+        <v>-4.12921269659595</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.38177975690148</v>
+        <v>-1.43829520205175</v>
       </c>
       <c r="F6" t="n">
-        <v>0.19032425805751</v>
+        <v>0.173986964592161</v>
       </c>
       <c r="G6" t="n">
-        <v>0.44265171507161</v>
+        <v>0.595587174417968</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.158963195433896</v>
+        <v>-1.37616818205542</v>
       </c>
       <c r="E7" t="n">
-        <v>0.053474672954099</v>
+        <v>-0.51176365249207</v>
       </c>
       <c r="F7" t="n">
-        <v>0.958166739098568</v>
+        <v>0.617398448711023</v>
       </c>
       <c r="G7" t="n">
-        <v>0.964465848514953</v>
+        <v>0.789066049137835</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.16810058815634</v>
+        <v>-3.7393438604026</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.41803778761443</v>
+        <v>-1.029894481975</v>
       </c>
       <c r="F8" t="n">
-        <v>0.179703408612331</v>
+        <v>0.321840949771728</v>
       </c>
       <c r="G8" t="n">
-        <v>0.44265171507161</v>
+        <v>0.595587174417968</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.37179484108536</v>
+        <v>-2.737178477482</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3365217465307</v>
+        <v>-1.02322555621373</v>
       </c>
       <c r="F9" t="n">
-        <v>0.204300791571512</v>
+        <v>0.32486573150071</v>
       </c>
       <c r="G9" t="n">
-        <v>0.44265171507161</v>
+        <v>0.595587174417968</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>4.29443168517916</v>
+        <v>1.15799433756615</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7162017371336</v>
+        <v>0.470779735755059</v>
       </c>
       <c r="F10" t="n">
-        <v>0.109842350206649</v>
+        <v>0.645599494749138</v>
       </c>
       <c r="G10" t="n">
-        <v>0.44265171507161</v>
+        <v>0.789066049137835</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.391857618716388</v>
+        <v>-0.0978362640647266</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.09136811892477</v>
+        <v>-0.0309031357107042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.928592984314635</v>
+        <v>0.975816200333687</v>
       </c>
       <c r="G11" t="n">
-        <v>0.964465848514953</v>
+        <v>0.975816200333687</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>7.34307840862006</v>
+        <v>2.93574629520819</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9402172438243</v>
+        <v>0.7616203622406</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0743578537255438</v>
+        <v>0.459881086663597</v>
       </c>
       <c r="G12" t="n">
-        <v>0.44265171507161</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.213692821677217</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.0675893172814093</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.947141049515616</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.964465848514953</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.125608712063541</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0454161459366648</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.964465848514953</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.964465848514953</v>
+        <v>0.722670279042796</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>49.2009422430207</v>
+        <v>89.4830019081012</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0754022156006</v>
+        <v>1.73004509632187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.301749017264913</v>
+        <v>0.107275065942664</v>
       </c>
       <c r="G2" t="n">
-        <v>0.653789537407312</v>
+        <v>0.447107075070866</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>49.1984273336599</v>
+        <v>27.2311685326936</v>
       </c>
       <c r="E3" t="n">
-        <v>0.797061565678297</v>
+        <v>0.233328402284103</v>
       </c>
       <c r="F3" t="n">
-        <v>0.439730774176384</v>
+        <v>0.819140190782423</v>
       </c>
       <c r="G3" t="n">
-        <v>0.714562508036625</v>
+        <v>0.911015167462711</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-76.9294267795553</v>
+        <v>-2.88875614191768</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.15660727433326</v>
+        <v>-0.0492473440399734</v>
       </c>
       <c r="F4" t="n">
-        <v>0.268245302906761</v>
+        <v>0.961470779061594</v>
       </c>
       <c r="G4" t="n">
-        <v>0.653789537407312</v>
+        <v>0.961470779061594</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-10.1070817988133</v>
+        <v>-82.6242413555406</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0778752406992111</v>
+        <v>-1.91199851722209</v>
       </c>
       <c r="F5" t="n">
-        <v>0.93911316998453</v>
+        <v>0.0781680968753364</v>
       </c>
       <c r="G5" t="n">
-        <v>0.93911316998453</v>
+        <v>0.447107075070866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>84.0662250081757</v>
+        <v>81.5484272789347</v>
       </c>
       <c r="E6" t="n">
-        <v>1.72247745549481</v>
+        <v>1.65279213981192</v>
       </c>
       <c r="F6" t="n">
-        <v>0.108671849018172</v>
+        <v>0.122306503086663</v>
       </c>
       <c r="G6" t="n">
-        <v>0.653789537407312</v>
+        <v>0.447107075070866</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>5.06132312704782</v>
+        <v>49.5679068572702</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0969831859169261</v>
+        <v>1.08536246263123</v>
       </c>
       <c r="F7" t="n">
-        <v>0.924218997902038</v>
+        <v>0.297478536101508</v>
       </c>
       <c r="G7" t="n">
-        <v>0.93911316998453</v>
+        <v>0.569988438819742</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>48.8983120814872</v>
+        <v>90.8067298332745</v>
       </c>
       <c r="E8" t="n">
-        <v>0.909225873056399</v>
+        <v>1.4804245044964</v>
       </c>
       <c r="F8" t="n">
-        <v>0.379779188796239</v>
+        <v>0.16258439093486</v>
       </c>
       <c r="G8" t="n">
-        <v>0.705304207764444</v>
+        <v>0.447107075070866</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>77.105792046982</v>
+        <v>27.2948902209842</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3431886093506</v>
+        <v>0.56582774933275</v>
       </c>
       <c r="F9" t="n">
-        <v>0.202190833629974</v>
+        <v>0.581146703129816</v>
       </c>
       <c r="G9" t="n">
-        <v>0.653789537407312</v>
+        <v>0.799118300376371</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-83.0859413908247</v>
+        <v>-24.3475285345493</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.93842623130359</v>
+        <v>-0.565781937293289</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0745945572984098</v>
+        <v>0.58117694572827</v>
       </c>
       <c r="G10" t="n">
-        <v>0.653789537407312</v>
+        <v>0.799118300376371</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>81.6111642556441</v>
+        <v>-12.2875835330168</v>
       </c>
       <c r="E11" t="n">
-        <v>1.13577500394544</v>
+        <v>-0.221432945391402</v>
       </c>
       <c r="F11" t="n">
-        <v>0.276556531390647</v>
+        <v>0.828195606784283</v>
       </c>
       <c r="G11" t="n">
-        <v>0.653789537407312</v>
+        <v>0.911015167462711</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>12.8510111175698</v>
+        <v>-70.0123002331567</v>
       </c>
       <c r="E12" t="n">
-        <v>0.170468051433501</v>
+        <v>-1.05440041448643</v>
       </c>
       <c r="F12" t="n">
-        <v>0.867266524929156</v>
+        <v>0.310902784810769</v>
       </c>
       <c r="G12" t="n">
-        <v>0.93911316998453</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-11.7091931785545</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.211229388947887</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.83598353093631</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.93911316998453</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-12.8162137458253</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.264577849642883</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.795483054424705</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.93911316998453</v>
+        <v>0.569988438819742</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>4.80810291893242</v>
+        <v>2.99684419475847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.564211022957085</v>
+        <v>0.240414952177087</v>
       </c>
       <c r="F2" t="n">
-        <v>0.583002473443491</v>
+        <v>0.814066705428918</v>
       </c>
       <c r="G2" t="n">
-        <v>0.68900292316049</v>
+        <v>0.895473375971809</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>11.6564593979345</v>
+        <v>17.6878380448794</v>
       </c>
       <c r="E3" t="n">
-        <v>0.746896283032792</v>
+        <v>0.877479081319264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.469508094349721</v>
+        <v>0.397454340724744</v>
       </c>
       <c r="G3" t="n">
-        <v>0.68900292316049</v>
+        <v>0.728666291328698</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.33899477534762</v>
+        <v>16.3590216584742</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0273057800771276</v>
+        <v>1.29015688740772</v>
       </c>
       <c r="F4" t="n">
-        <v>0.978664699090875</v>
+        <v>0.221303620843815</v>
       </c>
       <c r="G4" t="n">
-        <v>0.978664699090875</v>
+        <v>0.546797260631626</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>14.9475823581091</v>
+        <v>5.4723503816922</v>
       </c>
       <c r="E5" t="n">
-        <v>0.658341562776497</v>
+        <v>0.560529755712007</v>
       </c>
       <c r="F5" t="n">
-        <v>0.522749112609097</v>
+        <v>0.585431684863383</v>
       </c>
       <c r="G5" t="n">
-        <v>0.68900292316049</v>
+        <v>0.804968566687151</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-15.2974148232949</v>
+        <v>-15.1410026763387</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.65264629312484</v>
+        <v>-1.62640332057932</v>
       </c>
       <c r="F6" t="n">
-        <v>0.124307034325366</v>
+        <v>0.129819523009525</v>
       </c>
       <c r="G6" t="n">
-        <v>0.403997861557441</v>
+        <v>0.476004917701592</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>14.6783230291454</v>
+        <v>4.88575227021968</v>
       </c>
       <c r="E7" t="n">
-        <v>1.75529172154801</v>
+        <v>0.57281534196616</v>
       </c>
       <c r="F7" t="n">
-        <v>0.104679574560936</v>
+        <v>0.577345397568779</v>
       </c>
       <c r="G7" t="n">
-        <v>0.403997861557441</v>
+        <v>0.804968566687151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>10.9602864976899</v>
+        <v>-1.47191876685557</v>
       </c>
       <c r="E8" t="n">
-        <v>1.02888726372704</v>
+        <v>-0.124384172796035</v>
       </c>
       <c r="F8" t="n">
-        <v>0.323825536793829</v>
+        <v>0.903070402261745</v>
       </c>
       <c r="G8" t="n">
-        <v>0.68900292316049</v>
+        <v>0.903070402261745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.07425117651374</v>
+        <v>11.2438997086154</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.190486088554644</v>
+        <v>1.21279337745416</v>
       </c>
       <c r="F9" t="n">
-        <v>0.852112775932648</v>
+        <v>0.248544209378012</v>
       </c>
       <c r="G9" t="n">
-        <v>0.923122173927036</v>
+        <v>0.546797260631626</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>5.66182137181187</v>
+        <v>16.6353943656662</v>
       </c>
       <c r="E10" t="n">
-        <v>0.591439797608323</v>
+        <v>2.38083627113207</v>
       </c>
       <c r="F10" t="n">
-        <v>0.565201171444756</v>
+        <v>0.0347099073814305</v>
       </c>
       <c r="G10" t="n">
-        <v>0.68900292316049</v>
+        <v>0.245557203218764</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.2566754693027</v>
+        <v>-22.202940209598</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.782826316025106</v>
+        <v>-2.24186615727711</v>
       </c>
       <c r="F11" t="n">
-        <v>0.448902637216661</v>
+        <v>0.0446467642215935</v>
       </c>
       <c r="G11" t="n">
-        <v>0.68900292316049</v>
+        <v>0.245557203218764</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>17.7321041213777</v>
+        <v>-5.08322833198152</v>
       </c>
       <c r="E12" t="n">
-        <v>1.05102311728184</v>
+        <v>-0.416652365099863</v>
       </c>
       <c r="F12" t="n">
-        <v>0.313953571472852</v>
+        <v>0.684288723748656</v>
       </c>
       <c r="G12" t="n">
-        <v>0.68900292316049</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-21.9007688086182</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-2.23406671749563</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.045278185146015</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.294308203449098</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>18.3780804245953</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.25381291856563</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.0436957904146149</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.294308203449098</v>
+        <v>0.836352884581691</v>
       </c>
     </row>
   </sheetData>
@@ -2454,45 +2172,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2501,24 +2219,24 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8.64625200269644</v>
+        <v>7.47134685496238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -2527,24 +2245,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>11.6564593979345</v>
+        <v>11.2438997086154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2553,24 +2271,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>49.1984273336599</v>
+        <v>49.5679068572702</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2579,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2128.27249240115</v>
+        <v>1046.10887674005</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,24 +2323,24 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2228.65335542619</v>
+        <v>1556.84903954256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2631,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.25652010388715</v>
+        <v>2.93574629520819</v>
       </c>
     </row>
   </sheetData>
